--- a/docs/validacao-visual/2026-10-ficha-fabricante-designacao/vendas-designacao.xlsx
+++ b/docs/validacao-visual/2026-10-ficha-fabricante-designacao/vendas-designacao.xlsx
@@ -439,7 +439,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Gerado em: 26/10/2026, 11:03</v>
+        <v>Gerado em: 26/10/2026, 11:41</v>
       </c>
     </row>
     <row r="5">
